--- a/MainTop/1.06.2026 Макс Имена общее/по городам/название городов.xlsx
+++ b/MainTop/1.06.2026 Макс Имена общее/по городам/название городов.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Max\Documents\GitHub\Ozon_upload\MainTop\1.06.2026 Макс Имена общее\по городам\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DE795175-1381-457D-9B1C-6954A1DC4772}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{181525EE-0C6F-472F-B380-224C91FF9E7D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="28">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="27">
   <si>
     <t>г1</t>
   </si>
@@ -87,28 +87,25 @@
     <t>Воронеж</t>
   </si>
   <si>
-    <t>Ярославль</t>
-  </si>
-  <si>
-    <t>Краснодар</t>
-  </si>
-  <si>
     <t>Уфа</t>
   </si>
   <si>
-    <t>Саратов</t>
-  </si>
-  <si>
-    <t>Новосибирск</t>
-  </si>
-  <si>
     <t>Ростов</t>
   </si>
   <si>
     <t>Самара</t>
   </si>
   <si>
-    <t>Тюмень</t>
+    <t>Дальний Восток</t>
+  </si>
+  <si>
+    <t>Беларусь</t>
+  </si>
+  <si>
+    <t>Невинномысск</t>
+  </si>
+  <si>
+    <t>Пермь</t>
   </si>
 </sst>
 </file>
@@ -172,16 +169,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
@@ -514,46 +508,46 @@
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="B2" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="B2" s="3" t="s">
+      <c r="C2" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="D2" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="E2" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="F2" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="C2" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="D2" s="3" t="s">
+      <c r="G2" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="H2" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="I2" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="J2" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="K2" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="L2" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="M2" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="N2" s="3" t="s">
         <v>17</v>
-      </c>
-      <c r="E2" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="F2" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="G2" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="H2" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="I2" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="J2" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="K2" s="4" t="s">
-        <v>23</v>
-      </c>
-      <c r="L2" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="M2" s="4" t="s">
-        <v>25</v>
-      </c>
-      <c r="N2" s="4" t="s">
-        <v>26</v>
       </c>
     </row>
   </sheetData>
